--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\stefano\src\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830CAFB3-7A5C-4CF0-97D0-D3A24F789CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A634BD-D59C-44EC-8A6B-4EF126827C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="oXWj5iU3LtnvLpdhFqszSz/X91q3fG5U5zC5TJKtiGw="/>
     </ext>
   </extLst>
 </workbook>
@@ -80,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="221">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -915,6 +912,33 @@
   <si>
     <t>Al salvataggio del referto viene verificata la validità del codice fiscale, avvisando l'utente e permettendo una correzione per tempo. Qualora si dovesse incappare in questo errore lo stesso, viene mostrato il messaggio di errore a video e l'utente è invitato a controllare il codice fiscale per correggerlo. A quel punto può rigenerare il referto e ripetere la procedura.</t>
   </si>
+  <si>
+    <t>2026-03-20T12:08:49.039Z</t>
+  </si>
+  <si>
+    <t>fbf6c52ddfb0d6105fc1b02f7d69104b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.700261e95ee36ad94b40e3adab904b398048724a8c8c5396e2e40980a0365fcd.114ebc235c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>[ERRORE-11| L'elemento ClinicalDocument/recordTarget/patientRole/addr DEVE riportare i suoi sotto-elementi 'country', 'city' e 'streetAddressLine'.   ]</t>
+  </si>
+  <si>
+    <t>Questa problematica viene prevenuta da un controllo prima della generazione del referto: tutti i dati del paziente devono essere presenti e correttamente compilati. La gestione dell'errore è quindi di tipo preventivo.</t>
+  </si>
+  <si>
+    <t>L'applicazione non gestisce le immagini DICOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "effectivetime/low" ha sempre un valore di default, se non è presente la data perché non è disponbile  allora è presente il valore @nullFlavor = “UNK”.</t>
+  </si>
+  <si>
+    <t>La storia clinica non è gestita</t>
+  </si>
+  <si>
+    <t>Le allergie non vengono gestite</t>
+  </si>
 </sst>
 </file>
 
@@ -923,11 +947,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1061,7 +1092,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1370,174 +1401,221 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{565105C8-FFD6-432C-8B2E-BD1D172FCD26}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{816B634F-18CD-48D3-B461-04313602D5C7}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
@@ -2972,6 +3050,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W558"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3314,7 +3393,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" ht="145.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="31">
         <v>32</v>
       </c>
@@ -3410,7 +3489,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:23" ht="145.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31">
         <v>40</v>
       </c>
@@ -3504,7 +3583,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" ht="87.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
         <v>48</v>
       </c>
@@ -3602,7 +3681,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31">
         <v>78</v>
       </c>
@@ -3618,20 +3697,44 @@
       <c r="E17" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="33"/>
+      <c r="F17" s="32">
+        <v>46101</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>61</v>
+      </c>
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
+      <c r="M17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="P17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="R17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>216</v>
+      </c>
       <c r="T17" s="33"/>
       <c r="U17" s="34"/>
       <c r="V17" s="35"/>
@@ -3659,8 +3762,12 @@
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="37"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
+      <c r="J18" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>151</v>
+      </c>
       <c r="L18" s="33"/>
       <c r="M18" s="33"/>
       <c r="N18" s="33"/>
@@ -3696,8 +3803,12 @@
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
       <c r="I19" s="37"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
+      <c r="J19" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="K19" s="63" t="s">
+        <v>154</v>
+      </c>
       <c r="L19" s="33"/>
       <c r="M19" s="33"/>
       <c r="N19" s="33"/>
@@ -3733,8 +3844,12 @@
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="37"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
+      <c r="J20" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K20" s="63" t="s">
+        <v>154</v>
+      </c>
       <c r="L20" s="33"/>
       <c r="M20" s="33"/>
       <c r="N20" s="33"/>
@@ -3770,8 +3885,12 @@
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="37"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
+      <c r="J21" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K21" s="63" t="s">
+        <v>154</v>
+      </c>
       <c r="L21" s="33"/>
       <c r="M21" s="33"/>
       <c r="N21" s="33"/>
@@ -3807,8 +3926,12 @@
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
+      <c r="J22" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K22" s="63" t="s">
+        <v>154</v>
+      </c>
       <c r="L22" s="33"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
@@ -3881,8 +4004,12 @@
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="37"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
+      <c r="J24" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K24" s="63" t="s">
+        <v>154</v>
+      </c>
       <c r="L24" s="33"/>
       <c r="M24" s="33"/>
       <c r="N24" s="33"/>
@@ -3918,9 +4045,15 @@
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="37"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
+      <c r="J25" s="64" t="s">
+        <v>193</v>
+      </c>
+      <c r="K25" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="64" t="s">
+        <v>217</v>
+      </c>
       <c r="M25" s="33"/>
       <c r="N25" s="33"/>
       <c r="O25" s="33"/>
@@ -3955,9 +4088,15 @@
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="37"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
+      <c r="J26" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="L26" s="65" t="s">
+        <v>218</v>
+      </c>
       <c r="M26" s="33"/>
       <c r="N26" s="33"/>
       <c r="O26" s="33"/>
@@ -3992,9 +4131,15 @@
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
       <c r="I27" s="37"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
+      <c r="J27" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" s="66" t="s">
+        <v>219</v>
+      </c>
       <c r="M27" s="33"/>
       <c r="N27" s="33"/>
       <c r="O27" s="33"/>
@@ -4029,9 +4174,15 @@
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="37"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
+      <c r="J28" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="K28" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="L28" s="66" t="s">
+        <v>218</v>
+      </c>
       <c r="M28" s="33"/>
       <c r="N28" s="33"/>
       <c r="O28" s="33"/>
@@ -4066,9 +4217,15 @@
       <c r="G29" s="32"/>
       <c r="H29" s="32"/>
       <c r="I29" s="37"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
+      <c r="J29" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="K29" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="L29" s="67" t="s">
+        <v>220</v>
+      </c>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
       <c r="O29" s="33"/>
@@ -4103,8 +4260,12 @@
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
       <c r="I30" s="37"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
+      <c r="J30" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="K30" s="68" t="s">
+        <v>154</v>
+      </c>
       <c r="L30" s="33"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
@@ -4140,8 +4301,12 @@
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
       <c r="I31" s="37"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
+      <c r="J31" s="69" t="s">
+        <v>193</v>
+      </c>
+      <c r="K31" s="69" t="s">
+        <v>154</v>
+      </c>
       <c r="L31" s="33"/>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
@@ -4157,7 +4322,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="31">
         <v>152</v>
       </c>
@@ -4194,7 +4359,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="31">
         <v>154</v>
       </c>
@@ -4231,7 +4396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="31">
         <v>155</v>
       </c>
@@ -4268,7 +4433,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="31">
         <v>156</v>
       </c>
@@ -4305,7 +4470,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="31">
         <v>159</v>
       </c>
@@ -4342,7 +4507,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="31">
         <v>160</v>
       </c>
@@ -4379,7 +4544,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="31">
         <v>161</v>
       </c>
@@ -4416,7 +4581,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="31">
         <v>162</v>
       </c>
@@ -4453,7 +4618,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="31">
         <v>163</v>
       </c>
@@ -4490,7 +4655,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="31">
         <v>164</v>
       </c>
@@ -4527,7 +4692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="31">
         <v>165</v>
       </c>
@@ -4564,7 +4729,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="31">
         <v>166</v>
       </c>
@@ -4601,7 +4766,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="31">
         <v>167</v>
       </c>
@@ -4638,7 +4803,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="31">
         <v>168</v>
       </c>
@@ -4675,7 +4840,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="31">
         <v>169</v>
       </c>
@@ -4712,7 +4877,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:23" ht="131" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="31">
         <v>448</v>
       </c>
@@ -4749,7 +4914,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:23" ht="131" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="31">
         <v>449</v>
       </c>
@@ -4786,7 +4951,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="31">
         <v>461</v>
       </c>
@@ -4860,7 +5025,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="31">
         <v>468</v>
       </c>
@@ -5008,7 +5173,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="31">
         <v>475</v>
       </c>
@@ -8017,7 +8182,13 @@
       <c r="W558" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:W55" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A9:W55" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="RAD"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -8027,7 +8198,7 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
   </mergeCells>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -8038,7 +8209,7 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>J11:J55 M11:N55 P10:R55</xm:sqref>
+          <xm:sqref>P10:R55 M11:N55 J11:J55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
@@ -10335,6 +10506,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -10598,28 +10790,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10638,31 +10834,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\stefano\src\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A634BD-D59C-44EC-8A6B-4EF126827C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE558A-E04E-4DA5-A720-507FFD25082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Summary!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$32</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="188">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -350,9 +350,6 @@
     <t>RSA</t>
   </si>
   <si>
-    <t>VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
-  </si>
-  <si>
     <t>CERT_VAC</t>
   </si>
   <si>
@@ -411,9 +408,6 @@
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RAD_KO</t>
   </si>
   <si>
-    <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RSA_KO</t>
-  </si>
-  <si>
     <t>Per questo caso di test è richiesta la sola descrizione del comportamento a fronte di un timeout, da inserire nelle colonne relative a:
 "ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
   </si>
@@ -424,9 +418,6 @@
     <t>VALIDAZIONE_RAD_TIMEOUT</t>
   </si>
   <si>
-    <t>VALIDAZIONE_RSA_TIMEOUT</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_RAD_CT6_KO</t>
   </si>
   <si>
@@ -539,133 +530,7 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT6_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT8_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT9_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT10_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT13_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT14_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT15_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT16_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT17_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT18_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT19_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT20_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT21_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT22_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT23_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
     <t>RAP</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT24</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT25</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT26_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RAD_CT24_KO</t>
@@ -675,13 +540,6 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 24" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT27_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_RAD_CT25</t>
   </si>
   <si>
@@ -703,13 +561,6 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>VALIDAZIONE_CDA2_RSA_CT28_KO</t>
-  </si>
-  <si>
-    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
     <t>TPI</t>
   </si>
   <si>
@@ -938,6 +789,36 @@
   </si>
   <si>
     <t>Le allergie non vengono gestite</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.2e71011ce8b81d74e6f6b536e54630ced5e910562898f59cec3a186b47addbd4.19a2ced773^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-26T14:48:03.587Z</t>
+  </si>
+  <si>
+    <t>3f0be7c0a9dc5442f79757d231f6ec55</t>
+  </si>
+  <si>
+    <t>[ERRORE-b5| Sezione Referto: La sezione deve contenere l'elemento 'text'.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prima dell'invio del referto viene effettuata la validazione dei dati del referto,  permettendo una correzione prima dell'invio del referto. </t>
+  </si>
+  <si>
+    <t>Non è possibile selezionare un valore non ammesso</t>
+  </si>
+  <si>
+    <t>2026-03-26T15:05:44.710Z</t>
+  </si>
+  <si>
+    <t>5f240523db09769b2e1a112c74ac96ce</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.0fb1500ecf47cec8ffb9c5312b85ea027118c7e7e62869e4b2a17eaa97bcfe7f.7ae4522e1f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Il software non gestisce la storia clinica e le allegie</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1312,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1569,6 +1450,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1590,27 +1480,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3050,8 +2919,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:W558"/>
+  <dimension ref="A1:W535"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.453125" customWidth="1"/>
@@ -3091,12 +2959,12 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="54"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="57"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -3117,14 +2985,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="62" t="s">
-        <v>194</v>
-      </c>
-      <c r="D3" s="54"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="57"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -3145,12 +3013,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="58"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="62" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="54"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="57"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -3172,12 +3040,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="60"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="D5" s="54"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="57"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -3198,8 +3066,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -3354,37 +3222,37 @@
         <v>46098</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="I10" s="45"/>
       <c r="J10" s="46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
       <c r="M10" s="46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="P10" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q10" s="47" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="R10" s="47" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="S10" s="47" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="T10" s="47"/>
       <c r="U10" s="48"/>
@@ -3393,46 +3261,68 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="145.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="31">
-        <v>32</v>
-      </c>
-      <c r="B11" s="31" t="s">
+    <row r="11" spans="1:23" s="50" customFormat="1" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="41">
+        <v>39</v>
+      </c>
+      <c r="B11" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="33" t="s">
+      <c r="C11" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="44">
+        <v>46098</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="I11" s="45"/>
+      <c r="J11" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="P11" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q11" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="R11" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="S11" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="T11" s="47"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="50" customFormat="1" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" s="50" customFormat="1" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="41">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B12" s="41" t="s">
         <v>43</v>
@@ -3441,170 +3331,200 @@
         <v>50</v>
       </c>
       <c r="D12" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="43" t="s">
         <v>58</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>57</v>
       </c>
       <c r="F12" s="44">
         <v>46098</v>
       </c>
-      <c r="G12" s="44" t="s">
-        <v>202</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>201</v>
-      </c>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="45"/>
       <c r="J12" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
       <c r="M12" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="47" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="R12" s="47" t="s">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="S12" s="47" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="T12" s="47"/>
-      <c r="U12" s="48"/>
+      <c r="U12" s="48" t="s">
+        <v>59</v>
+      </c>
       <c r="V12" s="49"/>
       <c r="W12" s="47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="145.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31">
-        <v>40</v>
-      </c>
-      <c r="B13" s="31" t="s">
+    <row r="13" spans="1:23" s="50" customFormat="1" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="41">
+        <v>76</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="31" t="s">
+      <c r="C13" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="44">
+        <v>46098</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="I13" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="J13" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="33" t="s">
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="P13" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q13" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="R13" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="S13" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="T13" s="47"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="50" customFormat="1" ht="102" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="41">
+    <row r="14" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31">
+        <v>78</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="32">
+        <v>46101</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="P14" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q14" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="R14" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="S14" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="T14" s="33"/>
+      <c r="U14" s="34"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="44">
-        <v>46098</v>
-      </c>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="N14" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="O14" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="P14" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q14" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="R14" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="S14" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="T14" s="47"/>
-      <c r="U14" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="V14" s="49"/>
-      <c r="W14" s="47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="87.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="37"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
+      <c r="J15" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>108</v>
+      </c>
       <c r="L15" s="33"/>
       <c r="M15" s="33"/>
       <c r="N15" s="33"/>
@@ -3614,76 +3534,56 @@
       <c r="R15" s="33"/>
       <c r="S15" s="33"/>
       <c r="T15" s="33"/>
-      <c r="U15" s="34" t="s">
-        <v>61</v>
-      </c>
+      <c r="U15" s="34"/>
       <c r="V15" s="35"/>
       <c r="W15" s="33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="50" customFormat="1" ht="189" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="41">
-        <v>76</v>
-      </c>
-      <c r="B16" s="41" t="s">
+    <row r="16" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="31">
+        <v>80</v>
+      </c>
+      <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="44">
-        <v>46098</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="H16" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="I16" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="J16" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="O16" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="P16" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q16" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47" t="s">
-        <v>211</v>
-      </c>
-      <c r="T16" s="47"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="47" t="s">
+      <c r="D16" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>43</v>
@@ -3692,49 +3592,29 @@
         <v>50</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="32">
-        <v>46101</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>214</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="37"/>
       <c r="J17" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="K17" s="33"/>
+        <v>150</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>111</v>
+      </c>
       <c r="L17" s="33"/>
-      <c r="M17" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="N17" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="O17" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="P17" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q17" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="R17" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="S17" s="33" t="s">
-        <v>216</v>
-      </c>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
       <c r="T17" s="33"/>
       <c r="U17" s="34"/>
       <c r="V17" s="35"/>
@@ -3744,7 +3624,7 @@
     </row>
     <row r="18" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="31">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>43</v>
@@ -3753,20 +3633,20 @@
         <v>50</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="37"/>
       <c r="J18" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="K18" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
+      </c>
+      <c r="K18" s="51" t="s">
+        <v>111</v>
       </c>
       <c r="L18" s="33"/>
       <c r="M18" s="33"/>
@@ -3785,7 +3665,7 @@
     </row>
     <row r="19" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="31">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>43</v>
@@ -3794,20 +3674,20 @@
         <v>50</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
       <c r="I19" s="37"/>
-      <c r="J19" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="K19" s="63" t="s">
-        <v>154</v>
+      <c r="J19" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>111</v>
       </c>
       <c r="L19" s="33"/>
       <c r="M19" s="33"/>
@@ -3826,7 +3706,7 @@
     </row>
     <row r="20" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>43</v>
@@ -3835,29 +3715,49 @@
         <v>50</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="37"/>
+        <v>76</v>
+      </c>
+      <c r="F20" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>178</v>
+      </c>
       <c r="J20" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="K20" s="63" t="s">
-        <v>154</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K20" s="33"/>
       <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
+      <c r="M20" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="P20" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q20" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="R20" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="S20" s="51" t="s">
+        <v>182</v>
+      </c>
       <c r="T20" s="33"/>
       <c r="U20" s="34"/>
       <c r="V20" s="35"/>
@@ -3867,7 +3767,7 @@
     </row>
     <row r="21" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="31">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>43</v>
@@ -3876,20 +3776,20 @@
         <v>50</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="37"/>
       <c r="J21" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="K21" s="63" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>111</v>
       </c>
       <c r="L21" s="33"/>
       <c r="M21" s="33"/>
@@ -3906,9 +3806,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="31">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>43</v>
@@ -3917,22 +3817,24 @@
         <v>50</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="K22" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="L22" s="33"/>
+      <c r="J22" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="K22" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="L22" s="51" t="s">
+        <v>174</v>
+      </c>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="33"/>
@@ -3949,7 +3851,7 @@
     </row>
     <row r="23" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="31">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>43</v>
@@ -3958,18 +3860,24 @@
         <v>50</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
       <c r="I23" s="37"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
+      <c r="J23" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="L23" s="51" t="s">
+        <v>175</v>
+      </c>
       <c r="M23" s="33"/>
       <c r="N23" s="33"/>
       <c r="O23" s="33"/>
@@ -3986,7 +3894,7 @@
     </row>
     <row r="24" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="31">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>43</v>
@@ -3995,22 +3903,24 @@
         <v>50</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="37"/>
-      <c r="J24" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="K24" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="L24" s="33"/>
+      <c r="J24" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="L24" s="51" t="s">
+        <v>176</v>
+      </c>
       <c r="M24" s="33"/>
       <c r="N24" s="33"/>
       <c r="O24" s="33"/>
@@ -4025,9 +3935,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>43</v>
@@ -4036,23 +3946,23 @@
         <v>50</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="37"/>
-      <c r="J25" s="64" t="s">
-        <v>193</v>
-      </c>
-      <c r="K25" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="L25" s="64" t="s">
-        <v>217</v>
+      <c r="J25" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="L25" s="51" t="s">
+        <v>175</v>
       </c>
       <c r="M25" s="33"/>
       <c r="N25" s="33"/>
@@ -4070,7 +3980,7 @@
     </row>
     <row r="26" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>43</v>
@@ -4079,23 +3989,23 @@
         <v>50</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="37"/>
-      <c r="J26" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="K26" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="L26" s="65" t="s">
-        <v>218</v>
+      <c r="J26" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="K26" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="L26" s="52" t="s">
+        <v>177</v>
       </c>
       <c r="M26" s="33"/>
       <c r="N26" s="33"/>
@@ -4113,7 +4023,7 @@
     </row>
     <row r="27" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="31">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>43</v>
@@ -4122,24 +4032,22 @@
         <v>50</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
       <c r="I27" s="37"/>
-      <c r="J27" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="K27" s="66" t="s">
-        <v>156</v>
-      </c>
-      <c r="L27" s="66" t="s">
-        <v>219</v>
-      </c>
+      <c r="J27" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="K27" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="L27" s="33"/>
       <c r="M27" s="33"/>
       <c r="N27" s="33"/>
       <c r="O27" s="33"/>
@@ -4156,7 +4064,7 @@
     </row>
     <row r="28" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>43</v>
@@ -4165,24 +4073,22 @@
         <v>50</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="37"/>
-      <c r="J28" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="K28" s="66" t="s">
-        <v>156</v>
-      </c>
-      <c r="L28" s="66" t="s">
-        <v>218</v>
-      </c>
+      <c r="J28" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="K28" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="L28" s="33"/>
       <c r="M28" s="33"/>
       <c r="N28" s="33"/>
       <c r="O28" s="33"/>
@@ -4197,9 +4103,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="31">
-        <v>91</v>
+        <v>462</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>43</v>
@@ -4208,41 +4114,39 @@
         <v>50</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="K29" s="67" t="s">
-        <v>156</v>
-      </c>
-      <c r="L29" s="67" t="s">
-        <v>220</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K29" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="L29" s="31"/>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
+      <c r="O29" s="31"/>
       <c r="P29" s="33"/>
       <c r="Q29" s="33"/>
       <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
+      <c r="S29" s="31"/>
       <c r="T29" s="33"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="33" t="s">
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="31">
-        <v>92</v>
+        <v>471</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>43</v>
@@ -4251,21 +4155,27 @@
         <v>50</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="68" t="s">
-        <v>193</v>
-      </c>
-      <c r="K30" s="68" t="s">
-        <v>154</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="F30" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J30" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
@@ -4278,12 +4188,12 @@
       <c r="U30" s="34"/>
       <c r="V30" s="35"/>
       <c r="W30" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31">
-        <v>93</v>
+        <v>472</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>43</v>
@@ -4292,22 +4202,24 @@
         <v>50</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F31" s="32"/>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
       <c r="I31" s="37"/>
-      <c r="J31" s="69" t="s">
-        <v>193</v>
-      </c>
-      <c r="K31" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="L31" s="33"/>
+      <c r="J31" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K31" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L31" s="33" t="s">
+        <v>187</v>
+      </c>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
       <c r="O31" s="33"/>
@@ -4319,32 +4231,38 @@
       <c r="U31" s="34"/>
       <c r="V31" s="35"/>
       <c r="W31" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="31">
-        <v>152</v>
+        <v>474</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
       <c r="I32" s="37"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
+      <c r="J32" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>183</v>
+      </c>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
       <c r="O32" s="33"/>
@@ -4359,858 +4277,467 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="31">
-        <v>154</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="35"/>
-      <c r="W33" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="31">
-        <v>155</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="35"/>
-      <c r="W34" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="31">
-        <v>156</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="35"/>
-      <c r="W35" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="31">
-        <v>159</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="31">
-        <v>160</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="33"/>
-      <c r="T37" s="33"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="35"/>
-      <c r="W37" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="31">
-        <v>161</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="35"/>
-      <c r="W38" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="31">
-        <v>162</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="31">
-        <v>163</v>
-      </c>
-      <c r="B40" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="33"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="35"/>
-      <c r="W40" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="31">
-        <v>164</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E41" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="33"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="34"/>
-      <c r="V41" s="35"/>
-      <c r="W41" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="31">
-        <v>165</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="33"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="35"/>
-      <c r="W42" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="31">
-        <v>166</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="33"/>
-      <c r="T43" s="33"/>
-      <c r="U43" s="34"/>
-      <c r="V43" s="35"/>
-      <c r="W43" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="31">
-        <v>167</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="31">
-        <v>168</v>
-      </c>
-      <c r="B45" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="33"/>
-      <c r="M45" s="33"/>
-      <c r="N45" s="33"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="33"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="34"/>
-      <c r="V45" s="35"/>
-      <c r="W45" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="31">
-        <v>169</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
-      <c r="M46" s="33"/>
-      <c r="N46" s="33"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="33"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="34"/>
-      <c r="V46" s="35"/>
-      <c r="W46" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" ht="131" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="31">
-        <v>448</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="34"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" ht="131" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="31">
-        <v>449</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="34"/>
-      <c r="V48" s="35"/>
-      <c r="W48" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="31">
-        <v>461</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C49" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E49" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="31"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="31">
-        <v>462</v>
-      </c>
-      <c r="B50" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="E50" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="33"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="33"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="31">
-        <v>468</v>
-      </c>
-      <c r="B51" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="33"/>
-      <c r="N51" s="33"/>
-      <c r="O51" s="31"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="33"/>
-      <c r="S51" s="31"/>
-      <c r="T51" s="33"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="31">
-        <v>471</v>
-      </c>
-      <c r="B52" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E52" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="33"/>
-      <c r="M52" s="33"/>
-      <c r="N52" s="33"/>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="33"/>
-      <c r="S52" s="33"/>
-      <c r="T52" s="33"/>
-      <c r="U52" s="34"/>
-      <c r="V52" s="35"/>
-      <c r="W52" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="31">
-        <v>472</v>
-      </c>
-      <c r="B53" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="33"/>
-      <c r="M53" s="33"/>
-      <c r="N53" s="33"/>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="33"/>
-      <c r="T53" s="33"/>
-      <c r="U53" s="34"/>
-      <c r="V53" s="35"/>
-      <c r="W53" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="31">
-        <v>474</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E54" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="33"/>
-      <c r="O54" s="33"/>
-      <c r="P54" s="33"/>
-      <c r="Q54" s="33"/>
-      <c r="R54" s="33"/>
-      <c r="S54" s="33"/>
-      <c r="T54" s="33"/>
-      <c r="U54" s="34"/>
-      <c r="V54" s="35"/>
-      <c r="W54" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" ht="102" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="31">
-        <v>475</v>
-      </c>
-      <c r="B55" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="E55" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="37"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="33"/>
-      <c r="M55" s="33"/>
-      <c r="N55" s="33"/>
-      <c r="O55" s="33"/>
-      <c r="P55" s="33"/>
-      <c r="Q55" s="33"/>
-      <c r="R55" s="33"/>
-      <c r="S55" s="33"/>
-      <c r="T55" s="33"/>
-      <c r="U55" s="34"/>
-      <c r="V55" s="35"/>
-      <c r="W55" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="9"/>
+    </row>
+    <row r="34" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="9"/>
+    </row>
+    <row r="35" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="9"/>
+    </row>
+    <row r="36" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="9"/>
+    </row>
+    <row r="37" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="8"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="9"/>
+    </row>
+    <row r="38" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="8"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="9"/>
+    </row>
+    <row r="39" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="8"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="9"/>
+    </row>
+    <row r="40" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="9"/>
+    </row>
+    <row r="41" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="8"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="9"/>
+    </row>
+    <row r="42" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="8"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="9"/>
+    </row>
+    <row r="43" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="8"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="9"/>
+    </row>
+    <row r="44" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="8"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="9"/>
+    </row>
+    <row r="45" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="8"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="9"/>
+    </row>
+    <row r="46" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="8"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="9"/>
+    </row>
+    <row r="47" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="8"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="9"/>
+    </row>
+    <row r="48" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+      <c r="U48" s="8"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="9"/>
+    </row>
+    <row r="49" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+      <c r="U49" s="8"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="9"/>
+    </row>
+    <row r="50" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+      <c r="U50" s="8"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="9"/>
+    </row>
+    <row r="51" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="8"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="9"/>
+    </row>
+    <row r="52" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="8"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="9"/>
+    </row>
+    <row r="53" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="8"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="9"/>
+    </row>
+    <row r="54" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="8"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="9"/>
+    </row>
+    <row r="55" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="8"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="9"/>
+    </row>
+    <row r="56" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -5230,7 +4757,7 @@
       <c r="V56" s="2"/>
       <c r="W56" s="9"/>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -5250,7 +4777,7 @@
       <c r="V57" s="2"/>
       <c r="W57" s="9"/>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -5270,7 +4797,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="9"/>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -5290,7 +4817,7 @@
       <c r="V59" s="2"/>
       <c r="W59" s="9"/>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -5310,7 +4837,7 @@
       <c r="V60" s="2"/>
       <c r="W60" s="9"/>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -5330,7 +4857,7 @@
       <c r="V61" s="2"/>
       <c r="W61" s="9"/>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
@@ -5350,7 +4877,7 @@
       <c r="V62" s="2"/>
       <c r="W62" s="9"/>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -5370,7 +4897,7 @@
       <c r="V63" s="2"/>
       <c r="W63" s="9"/>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="6:23" x14ac:dyDescent="0.35">
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
@@ -6471,472 +5998,81 @@
       <c r="W118" s="9"/>
     </row>
     <row r="119" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="7"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="7"/>
-      <c r="Q119" s="7"/>
-      <c r="R119" s="7"/>
-      <c r="S119" s="7"/>
-      <c r="T119" s="7"/>
-      <c r="U119" s="8"/>
-      <c r="V119" s="2"/>
-      <c r="W119" s="9"/>
+      <c r="W119" s="7"/>
     </row>
     <row r="120" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="7"/>
-      <c r="S120" s="7"/>
-      <c r="T120" s="7"/>
-      <c r="U120" s="8"/>
-      <c r="V120" s="2"/>
-      <c r="W120" s="9"/>
+      <c r="W120" s="7"/>
     </row>
     <row r="121" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="7"/>
-      <c r="P121" s="7"/>
-      <c r="Q121" s="7"/>
-      <c r="R121" s="7"/>
-      <c r="S121" s="7"/>
-      <c r="T121" s="7"/>
-      <c r="U121" s="8"/>
-      <c r="V121" s="2"/>
-      <c r="W121" s="9"/>
+      <c r="W121" s="7"/>
     </row>
     <row r="122" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
-      <c r="O122" s="7"/>
-      <c r="P122" s="7"/>
-      <c r="Q122" s="7"/>
-      <c r="R122" s="7"/>
-      <c r="S122" s="7"/>
-      <c r="T122" s="7"/>
-      <c r="U122" s="8"/>
-      <c r="V122" s="2"/>
-      <c r="W122" s="9"/>
+      <c r="W122" s="7"/>
     </row>
     <row r="123" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
-      <c r="N123" s="7"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="7"/>
-      <c r="Q123" s="7"/>
-      <c r="R123" s="7"/>
-      <c r="S123" s="7"/>
-      <c r="T123" s="7"/>
-      <c r="U123" s="8"/>
-      <c r="V123" s="2"/>
-      <c r="W123" s="9"/>
+      <c r="W123" s="7"/>
     </row>
     <row r="124" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="7"/>
-      <c r="T124" s="7"/>
-      <c r="U124" s="8"/>
-      <c r="V124" s="2"/>
-      <c r="W124" s="9"/>
+      <c r="W124" s="7"/>
     </row>
     <row r="125" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="7"/>
-      <c r="T125" s="7"/>
-      <c r="U125" s="8"/>
-      <c r="V125" s="2"/>
-      <c r="W125" s="9"/>
+      <c r="W125" s="7"/>
     </row>
     <row r="126" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="7"/>
-      <c r="T126" s="7"/>
-      <c r="U126" s="8"/>
-      <c r="V126" s="2"/>
-      <c r="W126" s="9"/>
+      <c r="W126" s="7"/>
     </row>
     <row r="127" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="7"/>
-      <c r="S127" s="7"/>
-      <c r="T127" s="7"/>
-      <c r="U127" s="8"/>
-      <c r="V127" s="2"/>
-      <c r="W127" s="9"/>
+      <c r="W127" s="7"/>
     </row>
     <row r="128" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="7"/>
-      <c r="S128" s="7"/>
-      <c r="T128" s="7"/>
-      <c r="U128" s="8"/>
-      <c r="V128" s="2"/>
-      <c r="W128" s="9"/>
-    </row>
-    <row r="129" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="7"/>
-      <c r="S129" s="7"/>
-      <c r="T129" s="7"/>
-      <c r="U129" s="8"/>
-      <c r="V129" s="2"/>
-      <c r="W129" s="9"/>
-    </row>
-    <row r="130" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="7"/>
-      <c r="S130" s="7"/>
-      <c r="T130" s="7"/>
-      <c r="U130" s="8"/>
-      <c r="V130" s="2"/>
-      <c r="W130" s="9"/>
-    </row>
-    <row r="131" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="7"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7"/>
-      <c r="M131" s="7"/>
-      <c r="N131" s="7"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="7"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="7"/>
-      <c r="T131" s="7"/>
-      <c r="U131" s="8"/>
-      <c r="V131" s="2"/>
-      <c r="W131" s="9"/>
-    </row>
-    <row r="132" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="7"/>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="7"/>
-      <c r="S132" s="7"/>
-      <c r="T132" s="7"/>
-      <c r="U132" s="8"/>
-      <c r="V132" s="2"/>
-      <c r="W132" s="9"/>
-    </row>
-    <row r="133" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
-      <c r="N133" s="7"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="7"/>
-      <c r="T133" s="7"/>
-      <c r="U133" s="8"/>
-      <c r="V133" s="2"/>
-      <c r="W133" s="9"/>
-    </row>
-    <row r="134" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="7"/>
-      <c r="S134" s="7"/>
-      <c r="T134" s="7"/>
-      <c r="U134" s="8"/>
-      <c r="V134" s="2"/>
-      <c r="W134" s="9"/>
-    </row>
-    <row r="135" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="7"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="7"/>
-      <c r="N135" s="7"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="7"/>
-      <c r="Q135" s="7"/>
-      <c r="R135" s="7"/>
-      <c r="S135" s="7"/>
-      <c r="T135" s="7"/>
-      <c r="U135" s="8"/>
-      <c r="V135" s="2"/>
-      <c r="W135" s="9"/>
-    </row>
-    <row r="136" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="7"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="7"/>
-      <c r="T136" s="7"/>
-      <c r="U136" s="8"/>
-      <c r="V136" s="2"/>
-      <c r="W136" s="9"/>
-    </row>
-    <row r="137" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="7"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="7"/>
-      <c r="T137" s="7"/>
-      <c r="U137" s="8"/>
-      <c r="V137" s="2"/>
-      <c r="W137" s="9"/>
-    </row>
-    <row r="138" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="7"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
-      <c r="O138" s="7"/>
-      <c r="P138" s="7"/>
-      <c r="Q138" s="7"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="7"/>
-      <c r="T138" s="7"/>
-      <c r="U138" s="8"/>
-      <c r="V138" s="2"/>
-      <c r="W138" s="9"/>
-    </row>
-    <row r="139" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="7"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="7"/>
-      <c r="R139" s="7"/>
-      <c r="S139" s="7"/>
-      <c r="T139" s="7"/>
-      <c r="U139" s="8"/>
-      <c r="V139" s="2"/>
-      <c r="W139" s="9"/>
-    </row>
-    <row r="140" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="7"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="7"/>
-      <c r="Q140" s="7"/>
-      <c r="R140" s="7"/>
-      <c r="S140" s="7"/>
-      <c r="T140" s="7"/>
-      <c r="U140" s="8"/>
-      <c r="V140" s="2"/>
-      <c r="W140" s="9"/>
-    </row>
-    <row r="141" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="7"/>
-      <c r="K141" s="7"/>
-      <c r="L141" s="7"/>
-      <c r="M141" s="7"/>
-      <c r="N141" s="7"/>
-      <c r="O141" s="7"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="7"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="7"/>
-      <c r="T141" s="7"/>
-      <c r="U141" s="8"/>
-      <c r="V141" s="2"/>
-      <c r="W141" s="9"/>
-    </row>
-    <row r="142" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="W128" s="7"/>
+    </row>
+    <row r="129" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W129" s="7"/>
+    </row>
+    <row r="130" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W130" s="7"/>
+    </row>
+    <row r="131" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W131" s="7"/>
+    </row>
+    <row r="132" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W132" s="7"/>
+    </row>
+    <row r="133" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W133" s="7"/>
+    </row>
+    <row r="134" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W134" s="7"/>
+    </row>
+    <row r="135" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W135" s="7"/>
+    </row>
+    <row r="136" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W136" s="7"/>
+    </row>
+    <row r="137" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W137" s="7"/>
+    </row>
+    <row r="138" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W138" s="7"/>
+    </row>
+    <row r="139" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W139" s="7"/>
+    </row>
+    <row r="140" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W140" s="7"/>
+    </row>
+    <row r="141" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W141" s="7"/>
+    </row>
+    <row r="142" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="143" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="144" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W144" s="7"/>
     </row>
     <row r="145" spans="23:23" x14ac:dyDescent="0.35">
@@ -8112,83 +7248,8 @@
     <row r="535" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W535" s="7"/>
     </row>
-    <row r="536" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W536" s="7"/>
-    </row>
-    <row r="537" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W537" s="7"/>
-    </row>
-    <row r="538" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W538" s="7"/>
-    </row>
-    <row r="539" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W539" s="7"/>
-    </row>
-    <row r="540" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W540" s="7"/>
-    </row>
-    <row r="541" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W541" s="7"/>
-    </row>
-    <row r="542" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W542" s="7"/>
-    </row>
-    <row r="543" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W543" s="7"/>
-    </row>
-    <row r="544" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W544" s="7"/>
-    </row>
-    <row r="545" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W545" s="7"/>
-    </row>
-    <row r="546" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W546" s="7"/>
-    </row>
-    <row r="547" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W547" s="7"/>
-    </row>
-    <row r="548" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W548" s="7"/>
-    </row>
-    <row r="549" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W549" s="7"/>
-    </row>
-    <row r="550" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W550" s="7"/>
-    </row>
-    <row r="551" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W551" s="7"/>
-    </row>
-    <row r="552" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W552" s="7"/>
-    </row>
-    <row r="553" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W553" s="7"/>
-    </row>
-    <row r="554" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W554" s="7"/>
-    </row>
-    <row r="555" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W555" s="7"/>
-    </row>
-    <row r="556" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W556" s="7"/>
-    </row>
-    <row r="557" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W557" s="7"/>
-    </row>
-    <row r="558" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W558" s="7"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:W55" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="RAD"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A9:W32" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -8209,19 +7270,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>P10:R55 M11:N55 J11:J55</xm:sqref>
+          <xm:sqref>M21:N32 P21:R32 J11:J32 P10:R19 M11:N19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T10:T55</xm:sqref>
+          <xm:sqref>T10:T32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K55</xm:sqref>
+          <xm:sqref>K10:K32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8236,42 +7297,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -8295,22 +7356,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="G1" s="40" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8318,13 +7379,13 @@
         <v>44</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8332,13 +7393,13 @@
         <v>48</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8346,55 +7407,55 @@
         <v>50</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -8402,13 +7463,13 @@
         <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -8416,97 +7477,97 @@
         <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C15" s="12">
         <v>521</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9481,18 +8542,18 @@
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -10506,6 +9567,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
@@ -10515,15 +9585,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10791,6 +9852,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
@@ -10803,14 +9872,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\stefano\src\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\darcast\src\git-hub\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE558A-E04E-4DA5-A720-507FFD25082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F30AC82-67C2-47D9-95E2-39C7B53FE613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="187">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -804,9 +804,6 @@
   </si>
   <si>
     <t xml:space="preserve">Prima dell'invio del referto viene effettuata la validazione dei dati del referto,  permettendo una correzione prima dell'invio del referto. </t>
-  </si>
-  <si>
-    <t>Non è possibile selezionare un valore non ammesso</t>
   </si>
   <si>
     <t>2026-03-26T15:05:44.710Z</t>
@@ -1782,69 +1779,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="130.1796875" customWidth="1"/>
-    <col min="2" max="26" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="130.140625" customWidth="1"/>
+    <col min="2" max="26" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="87" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" ht="285" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
   </sheetData>
@@ -1856,27 +1853,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B996"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="194.1796875" customWidth="1"/>
-    <col min="3" max="6" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="194.140625" customWidth="1"/>
+    <col min="3" max="6" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>1</v>
       </c>
@@ -1884,7 +1881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -1892,7 +1889,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -1900,7 +1897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -1908,7 +1905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -1916,7 +1913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>6</v>
       </c>
@@ -1924,993 +1921,993 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -2920,24 +2917,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W535"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" customWidth="1"/>
-    <col min="2" max="2" width="46.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="63.81640625" customWidth="1"/>
-    <col min="5" max="5" width="104.81640625" customWidth="1"/>
-    <col min="6" max="9" width="33.1796875" customWidth="1"/>
-    <col min="10" max="10" width="27.1796875" customWidth="1"/>
-    <col min="11" max="18" width="36.453125" customWidth="1"/>
-    <col min="19" max="19" width="27.1796875" customWidth="1"/>
-    <col min="20" max="20" width="33.1796875" customWidth="1"/>
-    <col min="21" max="21" width="36.453125" customWidth="1"/>
-    <col min="22" max="23" width="31.81640625" customWidth="1"/>
-    <col min="27" max="27" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="63.85546875" customWidth="1"/>
+    <col min="5" max="5" width="104.85546875" customWidth="1"/>
+    <col min="6" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" customWidth="1"/>
+    <col min="11" max="18" width="36.42578125" customWidth="1"/>
+    <col min="19" max="19" width="27.140625" customWidth="1"/>
+    <col min="20" max="20" width="33.140625" customWidth="1"/>
+    <col min="21" max="21" width="36.42578125" customWidth="1"/>
+    <col min="22" max="23" width="31.85546875" customWidth="1"/>
+    <col min="27" max="27" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C1" s="4"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -2958,7 +2955,7 @@
       <c r="V1" s="2"/>
       <c r="W1" s="9"/>
     </row>
-    <row r="2" spans="1:23" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
         <v>18</v>
       </c>
@@ -2984,7 +2981,7 @@
       <c r="V2" s="2"/>
       <c r="W2" s="9"/>
     </row>
-    <row r="3" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>19</v>
       </c>
@@ -3012,7 +3009,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="61"/>
       <c r="B4" s="62"/>
       <c r="C4" s="65" t="s">
@@ -3039,7 +3036,7 @@
       <c r="V4" s="2"/>
       <c r="W4" s="9"/>
     </row>
-    <row r="5" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="63"/>
       <c r="B5" s="64"/>
       <c r="C5" s="65" t="s">
@@ -3065,7 +3062,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="9"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="54"/>
       <c r="B6" s="55"/>
       <c r="C6" s="10"/>
@@ -3088,7 +3085,7 @@
       <c r="V6" s="2"/>
       <c r="W6" s="9"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -3111,7 +3108,7 @@
       <c r="V7" s="2"/>
       <c r="W7" s="9"/>
     </row>
-    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -3131,7 +3128,7 @@
       <c r="V8" s="2"/>
       <c r="W8" s="9"/>
     </row>
-    <row r="9" spans="1:23" s="17" customFormat="1" ht="111.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:23" s="17" customFormat="1" ht="132" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>20</v>
       </c>
@@ -3202,7 +3199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="50" customFormat="1" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" s="50" customFormat="1" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>31</v>
       </c>
@@ -3261,7 +3258,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="50" customFormat="1" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" s="50" customFormat="1" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41">
         <v>39</v>
       </c>
@@ -3320,7 +3317,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="50" customFormat="1" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" s="50" customFormat="1" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>47</v>
       </c>
@@ -3377,7 +3374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="50" customFormat="1" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:23" s="50" customFormat="1" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>76</v>
       </c>
@@ -3438,7 +3435,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:23" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="31">
         <v>78</v>
       </c>
@@ -3499,7 +3496,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="31">
         <v>79</v>
       </c>
@@ -3540,7 +3537,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="31">
         <v>80</v>
       </c>
@@ -3581,7 +3578,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31">
         <v>81</v>
       </c>
@@ -3622,7 +3619,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31">
         <v>83</v>
       </c>
@@ -3663,7 +3660,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="31">
         <v>84</v>
       </c>
@@ -3704,7 +3701,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="31">
         <v>85</v>
       </c>
@@ -3765,7 +3762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="31">
         <v>86</v>
       </c>
@@ -3806,7 +3803,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="31">
         <v>87</v>
       </c>
@@ -3849,7 +3846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="31">
         <v>88</v>
       </c>
@@ -3892,7 +3889,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="31">
         <v>89</v>
       </c>
@@ -3935,7 +3932,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="31">
         <v>90</v>
       </c>
@@ -3978,7 +3975,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="31">
         <v>91</v>
       </c>
@@ -4021,7 +4018,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="31">
         <v>92</v>
       </c>
@@ -4062,7 +4059,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="31">
         <v>93</v>
       </c>
@@ -4103,7 +4100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="31">
         <v>462</v>
       </c>
@@ -4144,7 +4141,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="31">
         <v>471</v>
       </c>
@@ -4164,13 +4161,13 @@
         <v>46107</v>
       </c>
       <c r="G30" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="H30" s="32" t="s">
+      <c r="I30" s="37" t="s">
         <v>185</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>186</v>
       </c>
       <c r="J30" s="33" t="s">
         <v>59</v>
@@ -4191,7 +4188,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:23" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="31">
         <v>472</v>
       </c>
@@ -4218,7 +4215,7 @@
         <v>113</v>
       </c>
       <c r="L31" s="33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
@@ -4234,7 +4231,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31">
         <v>474</v>
       </c>
@@ -4260,9 +4257,7 @@
       <c r="K32" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="L32" s="33" t="s">
-        <v>183</v>
-      </c>
+      <c r="L32" s="33"/>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
       <c r="O32" s="33"/>
@@ -4277,7 +4272,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -4297,7 +4292,7 @@
       <c r="V33" s="2"/>
       <c r="W33" s="9"/>
     </row>
-    <row r="34" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -4317,7 +4312,7 @@
       <c r="V34" s="2"/>
       <c r="W34" s="9"/>
     </row>
-    <row r="35" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -4337,7 +4332,7 @@
       <c r="V35" s="2"/>
       <c r="W35" s="9"/>
     </row>
-    <row r="36" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -4357,7 +4352,7 @@
       <c r="V36" s="2"/>
       <c r="W36" s="9"/>
     </row>
-    <row r="37" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -4377,7 +4372,7 @@
       <c r="V37" s="2"/>
       <c r="W37" s="9"/>
     </row>
-    <row r="38" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -4397,7 +4392,7 @@
       <c r="V38" s="2"/>
       <c r="W38" s="9"/>
     </row>
-    <row r="39" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -4417,7 +4412,7 @@
       <c r="V39" s="2"/>
       <c r="W39" s="9"/>
     </row>
-    <row r="40" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -4437,7 +4432,7 @@
       <c r="V40" s="2"/>
       <c r="W40" s="9"/>
     </row>
-    <row r="41" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -4457,7 +4452,7 @@
       <c r="V41" s="2"/>
       <c r="W41" s="9"/>
     </row>
-    <row r="42" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -4477,7 +4472,7 @@
       <c r="V42" s="2"/>
       <c r="W42" s="9"/>
     </row>
-    <row r="43" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -4497,7 +4492,7 @@
       <c r="V43" s="2"/>
       <c r="W43" s="9"/>
     </row>
-    <row r="44" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -4517,7 +4512,7 @@
       <c r="V44" s="2"/>
       <c r="W44" s="9"/>
     </row>
-    <row r="45" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -4537,7 +4532,7 @@
       <c r="V45" s="2"/>
       <c r="W45" s="9"/>
     </row>
-    <row r="46" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -4557,7 +4552,7 @@
       <c r="V46" s="2"/>
       <c r="W46" s="9"/>
     </row>
-    <row r="47" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -4577,7 +4572,7 @@
       <c r="V47" s="2"/>
       <c r="W47" s="9"/>
     </row>
-    <row r="48" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -4597,7 +4592,7 @@
       <c r="V48" s="2"/>
       <c r="W48" s="9"/>
     </row>
-    <row r="49" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -4617,7 +4612,7 @@
       <c r="V49" s="2"/>
       <c r="W49" s="9"/>
     </row>
-    <row r="50" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
@@ -4637,7 +4632,7 @@
       <c r="V50" s="2"/>
       <c r="W50" s="9"/>
     </row>
-    <row r="51" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -4657,7 +4652,7 @@
       <c r="V51" s="2"/>
       <c r="W51" s="9"/>
     </row>
-    <row r="52" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -4677,7 +4672,7 @@
       <c r="V52" s="2"/>
       <c r="W52" s="9"/>
     </row>
-    <row r="53" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -4697,7 +4692,7 @@
       <c r="V53" s="2"/>
       <c r="W53" s="9"/>
     </row>
-    <row r="54" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -4717,7 +4712,7 @@
       <c r="V54" s="2"/>
       <c r="W54" s="9"/>
     </row>
-    <row r="55" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -4737,7 +4732,7 @@
       <c r="V55" s="2"/>
       <c r="W55" s="9"/>
     </row>
-    <row r="56" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -4757,7 +4752,7 @@
       <c r="V56" s="2"/>
       <c r="W56" s="9"/>
     </row>
-    <row r="57" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -4777,7 +4772,7 @@
       <c r="V57" s="2"/>
       <c r="W57" s="9"/>
     </row>
-    <row r="58" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -4797,7 +4792,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="9"/>
     </row>
-    <row r="59" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -4817,7 +4812,7 @@
       <c r="V59" s="2"/>
       <c r="W59" s="9"/>
     </row>
-    <row r="60" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -4837,7 +4832,7 @@
       <c r="V60" s="2"/>
       <c r="W60" s="9"/>
     </row>
-    <row r="61" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -4857,7 +4852,7 @@
       <c r="V61" s="2"/>
       <c r="W61" s="9"/>
     </row>
-    <row r="62" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
@@ -4877,7 +4872,7 @@
       <c r="V62" s="2"/>
       <c r="W62" s="9"/>
     </row>
-    <row r="63" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -4897,7 +4892,7 @@
       <c r="V63" s="2"/>
       <c r="W63" s="9"/>
     </row>
-    <row r="64" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
@@ -4917,7 +4912,7 @@
       <c r="V64" s="2"/>
       <c r="W64" s="9"/>
     </row>
-    <row r="65" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
@@ -4937,7 +4932,7 @@
       <c r="V65" s="2"/>
       <c r="W65" s="9"/>
     </row>
-    <row r="66" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="66" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
@@ -4957,7 +4952,7 @@
       <c r="V66" s="2"/>
       <c r="W66" s="9"/>
     </row>
-    <row r="67" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="67" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
@@ -4977,7 +4972,7 @@
       <c r="V67" s="2"/>
       <c r="W67" s="9"/>
     </row>
-    <row r="68" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
@@ -4997,7 +4992,7 @@
       <c r="V68" s="2"/>
       <c r="W68" s="9"/>
     </row>
-    <row r="69" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
@@ -5017,7 +5012,7 @@
       <c r="V69" s="2"/>
       <c r="W69" s="9"/>
     </row>
-    <row r="70" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
@@ -5037,7 +5032,7 @@
       <c r="V70" s="2"/>
       <c r="W70" s="9"/>
     </row>
-    <row r="71" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="71" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
@@ -5057,7 +5052,7 @@
       <c r="V71" s="2"/>
       <c r="W71" s="9"/>
     </row>
-    <row r="72" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="72" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="6"/>
@@ -5077,7 +5072,7 @@
       <c r="V72" s="2"/>
       <c r="W72" s="9"/>
     </row>
-    <row r="73" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="73" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
@@ -5097,7 +5092,7 @@
       <c r="V73" s="2"/>
       <c r="W73" s="9"/>
     </row>
-    <row r="74" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
@@ -5117,7 +5112,7 @@
       <c r="V74" s="2"/>
       <c r="W74" s="9"/>
     </row>
-    <row r="75" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="75" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
@@ -5137,7 +5132,7 @@
       <c r="V75" s="2"/>
       <c r="W75" s="9"/>
     </row>
-    <row r="76" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="76" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
@@ -5157,7 +5152,7 @@
       <c r="V76" s="2"/>
       <c r="W76" s="9"/>
     </row>
-    <row r="77" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
@@ -5177,7 +5172,7 @@
       <c r="V77" s="2"/>
       <c r="W77" s="9"/>
     </row>
-    <row r="78" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="78" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
@@ -5197,7 +5192,7 @@
       <c r="V78" s="2"/>
       <c r="W78" s="9"/>
     </row>
-    <row r="79" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="79" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
@@ -5217,7 +5212,7 @@
       <c r="V79" s="2"/>
       <c r="W79" s="9"/>
     </row>
-    <row r="80" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="80" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
@@ -5237,7 +5232,7 @@
       <c r="V80" s="2"/>
       <c r="W80" s="9"/>
     </row>
-    <row r="81" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="81" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
@@ -5257,7 +5252,7 @@
       <c r="V81" s="2"/>
       <c r="W81" s="9"/>
     </row>
-    <row r="82" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="82" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
@@ -5277,7 +5272,7 @@
       <c r="V82" s="2"/>
       <c r="W82" s="9"/>
     </row>
-    <row r="83" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="83" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
@@ -5297,7 +5292,7 @@
       <c r="V83" s="2"/>
       <c r="W83" s="9"/>
     </row>
-    <row r="84" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="84" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
@@ -5317,7 +5312,7 @@
       <c r="V84" s="2"/>
       <c r="W84" s="9"/>
     </row>
-    <row r="85" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="85" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
@@ -5337,7 +5332,7 @@
       <c r="V85" s="2"/>
       <c r="W85" s="9"/>
     </row>
-    <row r="86" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="86" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -5357,7 +5352,7 @@
       <c r="V86" s="2"/>
       <c r="W86" s="9"/>
     </row>
-    <row r="87" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="87" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -5377,7 +5372,7 @@
       <c r="V87" s="2"/>
       <c r="W87" s="9"/>
     </row>
-    <row r="88" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="88" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
@@ -5397,7 +5392,7 @@
       <c r="V88" s="2"/>
       <c r="W88" s="9"/>
     </row>
-    <row r="89" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="89" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
@@ -5417,7 +5412,7 @@
       <c r="V89" s="2"/>
       <c r="W89" s="9"/>
     </row>
-    <row r="90" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="90" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
@@ -5437,7 +5432,7 @@
       <c r="V90" s="2"/>
       <c r="W90" s="9"/>
     </row>
-    <row r="91" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="91" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
@@ -5457,7 +5452,7 @@
       <c r="V91" s="2"/>
       <c r="W91" s="9"/>
     </row>
-    <row r="92" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="92" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
@@ -5477,7 +5472,7 @@
       <c r="V92" s="2"/>
       <c r="W92" s="9"/>
     </row>
-    <row r="93" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="93" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
@@ -5497,7 +5492,7 @@
       <c r="V93" s="2"/>
       <c r="W93" s="9"/>
     </row>
-    <row r="94" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="94" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
@@ -5517,7 +5512,7 @@
       <c r="V94" s="2"/>
       <c r="W94" s="9"/>
     </row>
-    <row r="95" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="95" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
@@ -5537,7 +5532,7 @@
       <c r="V95" s="2"/>
       <c r="W95" s="9"/>
     </row>
-    <row r="96" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="96" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
@@ -5557,7 +5552,7 @@
       <c r="V96" s="2"/>
       <c r="W96" s="9"/>
     </row>
-    <row r="97" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="97" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
@@ -5577,7 +5572,7 @@
       <c r="V97" s="2"/>
       <c r="W97" s="9"/>
     </row>
-    <row r="98" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="98" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
@@ -5597,7 +5592,7 @@
       <c r="V98" s="2"/>
       <c r="W98" s="9"/>
     </row>
-    <row r="99" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="99" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
@@ -5617,7 +5612,7 @@
       <c r="V99" s="2"/>
       <c r="W99" s="9"/>
     </row>
-    <row r="100" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="100" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
@@ -5637,7 +5632,7 @@
       <c r="V100" s="2"/>
       <c r="W100" s="9"/>
     </row>
-    <row r="101" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="101" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
@@ -5657,7 +5652,7 @@
       <c r="V101" s="2"/>
       <c r="W101" s="9"/>
     </row>
-    <row r="102" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="102" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
@@ -5677,7 +5672,7 @@
       <c r="V102" s="2"/>
       <c r="W102" s="9"/>
     </row>
-    <row r="103" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="103" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
@@ -5697,7 +5692,7 @@
       <c r="V103" s="2"/>
       <c r="W103" s="9"/>
     </row>
-    <row r="104" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="104" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
@@ -5717,7 +5712,7 @@
       <c r="V104" s="2"/>
       <c r="W104" s="9"/>
     </row>
-    <row r="105" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="105" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
@@ -5737,7 +5732,7 @@
       <c r="V105" s="2"/>
       <c r="W105" s="9"/>
     </row>
-    <row r="106" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="106" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
@@ -5757,7 +5752,7 @@
       <c r="V106" s="2"/>
       <c r="W106" s="9"/>
     </row>
-    <row r="107" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="107" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
@@ -5777,7 +5772,7 @@
       <c r="V107" s="2"/>
       <c r="W107" s="9"/>
     </row>
-    <row r="108" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="108" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
@@ -5797,7 +5792,7 @@
       <c r="V108" s="2"/>
       <c r="W108" s="9"/>
     </row>
-    <row r="109" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="109" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
@@ -5817,7 +5812,7 @@
       <c r="V109" s="2"/>
       <c r="W109" s="9"/>
     </row>
-    <row r="110" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="110" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
@@ -5837,7 +5832,7 @@
       <c r="V110" s="2"/>
       <c r="W110" s="9"/>
     </row>
-    <row r="111" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="111" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
@@ -5857,7 +5852,7 @@
       <c r="V111" s="2"/>
       <c r="W111" s="9"/>
     </row>
-    <row r="112" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="112" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
@@ -5877,7 +5872,7 @@
       <c r="V112" s="2"/>
       <c r="W112" s="9"/>
     </row>
-    <row r="113" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="113" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
@@ -5897,7 +5892,7 @@
       <c r="V113" s="2"/>
       <c r="W113" s="9"/>
     </row>
-    <row r="114" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="114" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
@@ -5917,7 +5912,7 @@
       <c r="V114" s="2"/>
       <c r="W114" s="9"/>
     </row>
-    <row r="115" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="115" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
@@ -5937,7 +5932,7 @@
       <c r="V115" s="2"/>
       <c r="W115" s="9"/>
     </row>
-    <row r="116" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="116" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
@@ -5957,7 +5952,7 @@
       <c r="V116" s="2"/>
       <c r="W116" s="9"/>
     </row>
-    <row r="117" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="117" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
@@ -5977,7 +5972,7 @@
       <c r="V117" s="2"/>
       <c r="W117" s="9"/>
     </row>
-    <row r="118" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="118" spans="6:23" x14ac:dyDescent="0.25">
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
@@ -5997,1255 +5992,1255 @@
       <c r="V118" s="2"/>
       <c r="W118" s="9"/>
     </row>
-    <row r="119" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="119" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W119" s="7"/>
     </row>
-    <row r="120" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="120" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W120" s="7"/>
     </row>
-    <row r="121" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="121" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W121" s="7"/>
     </row>
-    <row r="122" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="122" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W122" s="7"/>
     </row>
-    <row r="123" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="123" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W123" s="7"/>
     </row>
-    <row r="124" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="124" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W124" s="7"/>
     </row>
-    <row r="125" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="125" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W125" s="7"/>
     </row>
-    <row r="126" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="126" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W126" s="7"/>
     </row>
-    <row r="127" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="127" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W127" s="7"/>
     </row>
-    <row r="128" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="128" spans="6:23" x14ac:dyDescent="0.25">
       <c r="W128" s="7"/>
     </row>
-    <row r="129" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="129" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W129" s="7"/>
     </row>
-    <row r="130" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="130" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W130" s="7"/>
     </row>
-    <row r="131" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="131" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W131" s="7"/>
     </row>
-    <row r="132" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="132" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W132" s="7"/>
     </row>
-    <row r="133" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="133" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W133" s="7"/>
     </row>
-    <row r="134" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="134" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W134" s="7"/>
     </row>
-    <row r="135" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="135" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W135" s="7"/>
     </row>
-    <row r="136" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="136" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W136" s="7"/>
     </row>
-    <row r="137" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="137" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W137" s="7"/>
     </row>
-    <row r="138" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="138" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W138" s="7"/>
     </row>
-    <row r="139" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="139" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W139" s="7"/>
     </row>
-    <row r="140" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="140" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W140" s="7"/>
     </row>
-    <row r="141" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="141" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W141" s="7"/>
     </row>
-    <row r="142" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="142" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="143" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="144" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W144" s="7"/>
     </row>
-    <row r="145" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="145" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W145" s="7"/>
     </row>
-    <row r="146" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="146" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W146" s="7"/>
     </row>
-    <row r="147" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="147" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W147" s="7"/>
     </row>
-    <row r="148" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="148" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W148" s="7"/>
     </row>
-    <row r="149" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="149" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W149" s="7"/>
     </row>
-    <row r="150" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="150" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W150" s="7"/>
     </row>
-    <row r="151" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="151" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W151" s="7"/>
     </row>
-    <row r="152" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="152" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W152" s="7"/>
     </row>
-    <row r="153" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="153" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W153" s="7"/>
     </row>
-    <row r="154" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="154" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W154" s="7"/>
     </row>
-    <row r="155" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="155" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W155" s="7"/>
     </row>
-    <row r="156" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="156" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W156" s="7"/>
     </row>
-    <row r="157" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="157" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W157" s="7"/>
     </row>
-    <row r="158" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="158" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W158" s="7"/>
     </row>
-    <row r="159" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="159" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W159" s="7"/>
     </row>
-    <row r="160" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="160" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W160" s="7"/>
     </row>
-    <row r="161" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="161" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W161" s="7"/>
     </row>
-    <row r="162" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="162" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W162" s="7"/>
     </row>
-    <row r="163" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="163" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W163" s="7"/>
     </row>
-    <row r="164" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="164" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W164" s="7"/>
     </row>
-    <row r="165" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="165" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W165" s="7"/>
     </row>
-    <row r="166" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="166" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W166" s="7"/>
     </row>
-    <row r="167" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="167" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="168" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W168" s="7"/>
     </row>
-    <row r="169" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="169" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W169" s="7"/>
     </row>
-    <row r="170" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="170" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W170" s="7"/>
     </row>
-    <row r="171" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="171" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W171" s="7"/>
     </row>
-    <row r="172" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="172" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="173" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W173" s="7"/>
     </row>
-    <row r="174" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="174" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W174" s="7"/>
     </row>
-    <row r="175" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="175" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W175" s="7"/>
     </row>
-    <row r="176" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="176" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W176" s="7"/>
     </row>
-    <row r="177" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="177" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W177" s="7"/>
     </row>
-    <row r="178" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="178" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W178" s="7"/>
     </row>
-    <row r="179" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="179" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W179" s="7"/>
     </row>
-    <row r="180" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="180" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W180" s="7"/>
     </row>
-    <row r="181" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="181" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W181" s="7"/>
     </row>
-    <row r="182" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="182" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W182" s="7"/>
     </row>
-    <row r="183" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="183" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W183" s="7"/>
     </row>
-    <row r="184" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="184" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W184" s="7"/>
     </row>
-    <row r="185" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="185" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W185" s="7"/>
     </row>
-    <row r="186" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="186" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W186" s="7"/>
     </row>
-    <row r="187" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="187" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W187" s="7"/>
     </row>
-    <row r="188" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="188" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W188" s="7"/>
     </row>
-    <row r="189" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="189" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W189" s="7"/>
     </row>
-    <row r="190" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="190" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W190" s="7"/>
     </row>
-    <row r="191" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="191" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W191" s="7"/>
     </row>
-    <row r="192" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="192" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W192" s="7"/>
     </row>
-    <row r="193" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="193" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W193" s="7"/>
     </row>
-    <row r="194" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="194" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W194" s="7"/>
     </row>
-    <row r="195" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="195" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W195" s="7"/>
     </row>
-    <row r="196" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="196" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W196" s="7"/>
     </row>
-    <row r="197" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="197" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W197" s="7"/>
     </row>
-    <row r="198" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="198" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W198" s="7"/>
     </row>
-    <row r="199" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="199" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W199" s="7"/>
     </row>
-    <row r="200" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="200" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W200" s="7"/>
     </row>
-    <row r="201" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="201" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W201" s="7"/>
     </row>
-    <row r="202" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="202" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W202" s="7"/>
     </row>
-    <row r="203" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="203" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W203" s="7"/>
     </row>
-    <row r="204" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="204" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W204" s="7"/>
     </row>
-    <row r="205" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="205" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W205" s="7"/>
     </row>
-    <row r="206" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="206" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W206" s="7"/>
     </row>
-    <row r="207" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="207" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W207" s="7"/>
     </row>
-    <row r="208" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="208" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W208" s="7"/>
     </row>
-    <row r="209" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="209" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W209" s="7"/>
     </row>
-    <row r="210" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="210" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W210" s="7"/>
     </row>
-    <row r="211" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="211" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W211" s="7"/>
     </row>
-    <row r="212" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="212" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W212" s="7"/>
     </row>
-    <row r="213" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="213" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W213" s="7"/>
     </row>
-    <row r="214" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="214" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W214" s="7"/>
     </row>
-    <row r="215" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="215" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W215" s="7"/>
     </row>
-    <row r="216" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="216" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W216" s="7"/>
     </row>
-    <row r="217" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="217" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W217" s="7"/>
     </row>
-    <row r="218" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="218" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W218" s="7"/>
     </row>
-    <row r="219" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="219" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W219" s="7"/>
     </row>
-    <row r="220" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="220" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W220" s="7"/>
     </row>
-    <row r="221" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="221" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W221" s="7"/>
     </row>
-    <row r="222" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="222" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W222" s="7"/>
     </row>
-    <row r="223" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="223" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W223" s="7"/>
     </row>
-    <row r="224" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="224" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W224" s="7"/>
     </row>
-    <row r="225" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="225" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W225" s="7"/>
     </row>
-    <row r="226" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="226" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W226" s="7"/>
     </row>
-    <row r="227" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="227" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W227" s="7"/>
     </row>
-    <row r="228" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="228" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W228" s="7"/>
     </row>
-    <row r="229" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="229" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W229" s="7"/>
     </row>
-    <row r="230" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="230" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W230" s="7"/>
     </row>
-    <row r="231" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="231" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W231" s="7"/>
     </row>
-    <row r="232" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="232" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W232" s="7"/>
     </row>
-    <row r="233" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="233" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W233" s="7"/>
     </row>
-    <row r="234" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="234" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W234" s="7"/>
     </row>
-    <row r="235" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="235" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W235" s="7"/>
     </row>
-    <row r="236" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="236" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W236" s="7"/>
     </row>
-    <row r="237" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="237" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W237" s="7"/>
     </row>
-    <row r="238" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="238" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W238" s="7"/>
     </row>
-    <row r="239" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="239" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W239" s="7"/>
     </row>
-    <row r="240" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="240" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W240" s="7"/>
     </row>
-    <row r="241" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="241" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W241" s="7"/>
     </row>
-    <row r="242" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="242" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W242" s="7"/>
     </row>
-    <row r="243" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="243" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W243" s="7"/>
     </row>
-    <row r="244" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="244" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W244" s="7"/>
     </row>
-    <row r="245" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="245" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W245" s="7"/>
     </row>
-    <row r="246" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="246" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W246" s="7"/>
     </row>
-    <row r="247" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="247" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W247" s="7"/>
     </row>
-    <row r="248" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="248" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W248" s="7"/>
     </row>
-    <row r="249" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="249" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W249" s="7"/>
     </row>
-    <row r="250" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="250" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W250" s="7"/>
     </row>
-    <row r="251" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="251" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W251" s="7"/>
     </row>
-    <row r="252" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="252" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W252" s="7"/>
     </row>
-    <row r="253" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="253" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W253" s="7"/>
     </row>
-    <row r="254" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="254" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W254" s="7"/>
     </row>
-    <row r="255" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="255" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W255" s="7"/>
     </row>
-    <row r="256" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="256" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W256" s="7"/>
     </row>
-    <row r="257" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="257" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W257" s="7"/>
     </row>
-    <row r="258" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="258" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W258" s="7"/>
     </row>
-    <row r="259" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="259" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W259" s="7"/>
     </row>
-    <row r="260" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="260" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W260" s="7"/>
     </row>
-    <row r="261" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="261" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W261" s="7"/>
     </row>
-    <row r="262" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="262" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W262" s="7"/>
     </row>
-    <row r="263" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="263" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W263" s="7"/>
     </row>
-    <row r="264" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="264" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W264" s="7"/>
     </row>
-    <row r="265" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="265" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W265" s="7"/>
     </row>
-    <row r="266" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="266" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W266" s="7"/>
     </row>
-    <row r="267" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="267" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W267" s="7"/>
     </row>
-    <row r="268" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="268" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W268" s="7"/>
     </row>
-    <row r="269" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="269" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W269" s="7"/>
     </row>
-    <row r="270" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="270" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W270" s="7"/>
     </row>
-    <row r="271" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="271" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W271" s="7"/>
     </row>
-    <row r="272" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="272" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W272" s="7"/>
     </row>
-    <row r="273" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="273" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W273" s="7"/>
     </row>
-    <row r="274" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="274" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W274" s="7"/>
     </row>
-    <row r="275" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="275" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W275" s="7"/>
     </row>
-    <row r="276" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="276" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W276" s="7"/>
     </row>
-    <row r="277" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="277" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W277" s="7"/>
     </row>
-    <row r="278" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="278" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W278" s="7"/>
     </row>
-    <row r="279" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="279" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W279" s="7"/>
     </row>
-    <row r="280" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="280" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W280" s="7"/>
     </row>
-    <row r="281" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="281" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W281" s="7"/>
     </row>
-    <row r="282" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="282" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W282" s="7"/>
     </row>
-    <row r="283" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="283" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W283" s="7"/>
     </row>
-    <row r="284" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="284" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W284" s="7"/>
     </row>
-    <row r="285" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="285" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W285" s="7"/>
     </row>
-    <row r="286" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="286" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W286" s="7"/>
     </row>
-    <row r="287" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="287" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W287" s="7"/>
     </row>
-    <row r="288" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="288" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W288" s="7"/>
     </row>
-    <row r="289" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="289" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W289" s="7"/>
     </row>
-    <row r="290" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="290" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W290" s="7"/>
     </row>
-    <row r="291" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="291" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W291" s="7"/>
     </row>
-    <row r="292" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="292" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W292" s="7"/>
     </row>
-    <row r="293" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="293" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W293" s="7"/>
     </row>
-    <row r="294" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="294" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W294" s="7"/>
     </row>
-    <row r="295" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="295" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W295" s="7"/>
     </row>
-    <row r="296" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="296" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W296" s="7"/>
     </row>
-    <row r="297" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="297" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W297" s="7"/>
     </row>
-    <row r="298" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="298" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W298" s="7"/>
     </row>
-    <row r="299" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="299" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W299" s="7"/>
     </row>
-    <row r="300" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="300" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W300" s="7"/>
     </row>
-    <row r="301" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="301" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W301" s="7"/>
     </row>
-    <row r="302" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="302" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W302" s="7"/>
     </row>
-    <row r="303" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="303" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W303" s="7"/>
     </row>
-    <row r="304" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="304" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W304" s="7"/>
     </row>
-    <row r="305" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="305" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W305" s="7"/>
     </row>
-    <row r="306" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="306" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W306" s="7"/>
     </row>
-    <row r="307" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="307" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W307" s="7"/>
     </row>
-    <row r="308" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="308" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W308" s="7"/>
     </row>
-    <row r="309" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="309" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W309" s="7"/>
     </row>
-    <row r="310" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="310" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W310" s="7"/>
     </row>
-    <row r="311" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="311" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W311" s="7"/>
     </row>
-    <row r="312" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="312" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W312" s="7"/>
     </row>
-    <row r="313" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="313" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W313" s="7"/>
     </row>
-    <row r="314" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="314" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W314" s="7"/>
     </row>
-    <row r="315" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="315" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W315" s="7"/>
     </row>
-    <row r="316" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="316" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W316" s="7"/>
     </row>
-    <row r="317" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="317" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W317" s="7"/>
     </row>
-    <row r="318" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="318" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W318" s="7"/>
     </row>
-    <row r="319" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="319" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W319" s="7"/>
     </row>
-    <row r="320" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="320" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W320" s="7"/>
     </row>
-    <row r="321" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="321" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W321" s="7"/>
     </row>
-    <row r="322" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="322" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W322" s="7"/>
     </row>
-    <row r="323" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="323" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W323" s="7"/>
     </row>
-    <row r="324" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="324" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W324" s="7"/>
     </row>
-    <row r="325" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="325" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W325" s="7"/>
     </row>
-    <row r="326" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="326" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W326" s="7"/>
     </row>
-    <row r="327" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="327" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W327" s="7"/>
     </row>
-    <row r="328" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="328" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W328" s="7"/>
     </row>
-    <row r="329" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="329" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W329" s="7"/>
     </row>
-    <row r="330" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="330" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W330" s="7"/>
     </row>
-    <row r="331" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="331" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W331" s="7"/>
     </row>
-    <row r="332" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="332" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W332" s="7"/>
     </row>
-    <row r="333" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="333" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W333" s="7"/>
     </row>
-    <row r="334" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="334" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W334" s="7"/>
     </row>
-    <row r="335" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="335" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W335" s="7"/>
     </row>
-    <row r="336" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="336" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W336" s="7"/>
     </row>
-    <row r="337" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="337" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W337" s="7"/>
     </row>
-    <row r="338" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="338" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W338" s="7"/>
     </row>
-    <row r="339" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="339" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W339" s="7"/>
     </row>
-    <row r="340" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="340" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W340" s="7"/>
     </row>
-    <row r="341" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="341" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W341" s="7"/>
     </row>
-    <row r="342" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="342" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W342" s="7"/>
     </row>
-    <row r="343" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="343" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W343" s="7"/>
     </row>
-    <row r="344" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="344" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W344" s="7"/>
     </row>
-    <row r="345" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="345" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W345" s="7"/>
     </row>
-    <row r="346" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="346" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W346" s="7"/>
     </row>
-    <row r="347" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="347" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W347" s="7"/>
     </row>
-    <row r="348" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="348" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W348" s="7"/>
     </row>
-    <row r="349" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="349" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W349" s="7"/>
     </row>
-    <row r="350" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="350" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W350" s="7"/>
     </row>
-    <row r="351" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="351" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W351" s="7"/>
     </row>
-    <row r="352" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="352" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W352" s="7"/>
     </row>
-    <row r="353" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="353" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W353" s="7"/>
     </row>
-    <row r="354" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="354" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W354" s="7"/>
     </row>
-    <row r="355" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="355" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W355" s="7"/>
     </row>
-    <row r="356" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="356" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W356" s="7"/>
     </row>
-    <row r="357" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="357" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W357" s="7"/>
     </row>
-    <row r="358" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="358" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W358" s="7"/>
     </row>
-    <row r="359" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="359" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W359" s="7"/>
     </row>
-    <row r="360" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="360" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W360" s="7"/>
     </row>
-    <row r="361" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="361" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W361" s="7"/>
     </row>
-    <row r="362" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="362" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W362" s="7"/>
     </row>
-    <row r="363" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="363" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W363" s="7"/>
     </row>
-    <row r="364" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="364" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W364" s="7"/>
     </row>
-    <row r="365" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="365" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W365" s="7"/>
     </row>
-    <row r="366" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="366" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W366" s="7"/>
     </row>
-    <row r="367" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="367" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W367" s="7"/>
     </row>
-    <row r="368" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="368" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W368" s="7"/>
     </row>
-    <row r="369" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="369" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W369" s="7"/>
     </row>
-    <row r="370" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="370" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W370" s="7"/>
     </row>
-    <row r="371" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="371" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W371" s="7"/>
     </row>
-    <row r="372" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="372" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W372" s="7"/>
     </row>
-    <row r="373" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="373" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W373" s="7"/>
     </row>
-    <row r="374" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="374" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W374" s="7"/>
     </row>
-    <row r="375" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="375" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W375" s="7"/>
     </row>
-    <row r="376" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="376" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W376" s="7"/>
     </row>
-    <row r="377" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="377" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W377" s="7"/>
     </row>
-    <row r="378" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="378" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W378" s="7"/>
     </row>
-    <row r="379" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="379" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W379" s="7"/>
     </row>
-    <row r="380" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="380" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W380" s="7"/>
     </row>
-    <row r="381" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="381" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W381" s="7"/>
     </row>
-    <row r="382" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="382" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W382" s="7"/>
     </row>
-    <row r="383" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="383" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W383" s="7"/>
     </row>
-    <row r="384" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="384" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W384" s="7"/>
     </row>
-    <row r="385" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="385" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W385" s="7"/>
     </row>
-    <row r="386" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="386" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W386" s="7"/>
     </row>
-    <row r="387" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="387" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W387" s="7"/>
     </row>
-    <row r="388" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="388" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W388" s="7"/>
     </row>
-    <row r="389" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="389" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W389" s="7"/>
     </row>
-    <row r="390" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="390" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W390" s="7"/>
     </row>
-    <row r="391" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="391" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W391" s="7"/>
     </row>
-    <row r="392" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="392" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W392" s="7"/>
     </row>
-    <row r="393" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="393" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W393" s="7"/>
     </row>
-    <row r="394" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="394" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W394" s="7"/>
     </row>
-    <row r="395" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="395" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W395" s="7"/>
     </row>
-    <row r="396" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="396" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W396" s="7"/>
     </row>
-    <row r="397" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="397" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W397" s="7"/>
     </row>
-    <row r="398" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="398" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W398" s="7"/>
     </row>
-    <row r="399" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="399" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W399" s="7"/>
     </row>
-    <row r="400" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="400" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W400" s="7"/>
     </row>
-    <row r="401" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="401" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W401" s="7"/>
     </row>
-    <row r="402" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="402" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W402" s="7"/>
     </row>
-    <row r="403" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="403" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W403" s="7"/>
     </row>
-    <row r="404" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="404" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W404" s="7"/>
     </row>
-    <row r="405" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="405" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W405" s="7"/>
     </row>
-    <row r="406" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="406" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W406" s="7"/>
     </row>
-    <row r="407" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="407" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W407" s="7"/>
     </row>
-    <row r="408" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="408" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W408" s="7"/>
     </row>
-    <row r="409" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="409" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W409" s="7"/>
     </row>
-    <row r="410" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="410" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W410" s="7"/>
     </row>
-    <row r="411" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="411" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W411" s="7"/>
     </row>
-    <row r="412" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="412" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W412" s="7"/>
     </row>
-    <row r="413" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="413" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W413" s="7"/>
     </row>
-    <row r="414" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="414" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W414" s="7"/>
     </row>
-    <row r="415" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="415" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W415" s="7"/>
     </row>
-    <row r="416" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="416" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W416" s="7"/>
     </row>
-    <row r="417" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="417" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W417" s="7"/>
     </row>
-    <row r="418" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="418" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W418" s="7"/>
     </row>
-    <row r="419" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="419" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W419" s="7"/>
     </row>
-    <row r="420" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="420" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W420" s="7"/>
     </row>
-    <row r="421" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="421" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W421" s="7"/>
     </row>
-    <row r="422" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="422" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W422" s="7"/>
     </row>
-    <row r="423" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="423" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W423" s="7"/>
     </row>
-    <row r="424" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="424" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W424" s="7"/>
     </row>
-    <row r="425" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="425" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W425" s="7"/>
     </row>
-    <row r="426" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="426" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W426" s="7"/>
     </row>
-    <row r="427" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="427" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W427" s="7"/>
     </row>
-    <row r="428" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="428" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W428" s="7"/>
     </row>
-    <row r="429" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="429" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W429" s="7"/>
     </row>
-    <row r="430" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="430" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W430" s="7"/>
     </row>
-    <row r="431" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="431" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W431" s="7"/>
     </row>
-    <row r="432" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="432" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W432" s="7"/>
     </row>
-    <row r="433" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="433" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W433" s="7"/>
     </row>
-    <row r="434" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="434" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W434" s="7"/>
     </row>
-    <row r="435" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="435" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W435" s="7"/>
     </row>
-    <row r="436" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="436" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W436" s="7"/>
     </row>
-    <row r="437" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="437" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W437" s="7"/>
     </row>
-    <row r="438" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="438" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W438" s="7"/>
     </row>
-    <row r="439" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="439" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W439" s="7"/>
     </row>
-    <row r="440" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="440" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W440" s="7"/>
     </row>
-    <row r="441" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="441" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W441" s="7"/>
     </row>
-    <row r="442" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="442" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W442" s="7"/>
     </row>
-    <row r="443" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="443" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W443" s="7"/>
     </row>
-    <row r="444" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="444" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W444" s="7"/>
     </row>
-    <row r="445" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="445" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W445" s="7"/>
     </row>
-    <row r="446" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="446" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W446" s="7"/>
     </row>
-    <row r="447" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="447" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W447" s="7"/>
     </row>
-    <row r="448" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="448" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W448" s="7"/>
     </row>
-    <row r="449" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="449" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W449" s="7"/>
     </row>
-    <row r="450" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="450" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W450" s="7"/>
     </row>
-    <row r="451" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="451" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W451" s="7"/>
     </row>
-    <row r="452" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="452" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W452" s="7"/>
     </row>
-    <row r="453" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="453" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W453" s="7"/>
     </row>
-    <row r="454" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="454" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W454" s="7"/>
     </row>
-    <row r="455" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="455" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W455" s="7"/>
     </row>
-    <row r="456" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="456" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W456" s="7"/>
     </row>
-    <row r="457" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="457" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W457" s="7"/>
     </row>
-    <row r="458" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="458" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W458" s="7"/>
     </row>
-    <row r="459" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="459" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W459" s="7"/>
     </row>
-    <row r="460" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="460" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W460" s="7"/>
     </row>
-    <row r="461" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="461" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W461" s="7"/>
     </row>
-    <row r="462" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="462" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W462" s="7"/>
     </row>
-    <row r="463" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="463" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W463" s="7"/>
     </row>
-    <row r="464" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="464" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W464" s="7"/>
     </row>
-    <row r="465" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="465" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W465" s="7"/>
     </row>
-    <row r="466" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="466" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W466" s="7"/>
     </row>
-    <row r="467" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="467" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W467" s="7"/>
     </row>
-    <row r="468" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="468" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W468" s="7"/>
     </row>
-    <row r="469" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="469" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W469" s="7"/>
     </row>
-    <row r="470" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="470" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W470" s="7"/>
     </row>
-    <row r="471" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="471" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W471" s="7"/>
     </row>
-    <row r="472" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="472" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W472" s="7"/>
     </row>
-    <row r="473" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="473" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W473" s="7"/>
     </row>
-    <row r="474" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="474" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W474" s="7"/>
     </row>
-    <row r="475" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="475" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W475" s="7"/>
     </row>
-    <row r="476" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="476" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W476" s="7"/>
     </row>
-    <row r="477" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="477" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W477" s="7"/>
     </row>
-    <row r="478" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="478" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W478" s="7"/>
     </row>
-    <row r="479" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="479" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W479" s="7"/>
     </row>
-    <row r="480" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="480" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W480" s="7"/>
     </row>
-    <row r="481" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="481" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W481" s="7"/>
     </row>
-    <row r="482" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="482" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W482" s="7"/>
     </row>
-    <row r="483" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="483" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W483" s="7"/>
     </row>
-    <row r="484" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="484" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W484" s="7"/>
     </row>
-    <row r="485" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="485" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W485" s="7"/>
     </row>
-    <row r="486" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="486" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W486" s="7"/>
     </row>
-    <row r="487" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="487" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W487" s="7"/>
     </row>
-    <row r="488" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="488" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W488" s="7"/>
     </row>
-    <row r="489" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="489" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W489" s="7"/>
     </row>
-    <row r="490" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="490" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W490" s="7"/>
     </row>
-    <row r="491" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="491" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W491" s="7"/>
     </row>
-    <row r="492" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="492" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W492" s="7"/>
     </row>
-    <row r="493" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="493" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W493" s="7"/>
     </row>
-    <row r="494" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="494" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W494" s="7"/>
     </row>
-    <row r="495" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="495" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W495" s="7"/>
     </row>
-    <row r="496" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="496" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W496" s="7"/>
     </row>
-    <row r="497" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="497" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W497" s="7"/>
     </row>
-    <row r="498" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="498" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W498" s="7"/>
     </row>
-    <row r="499" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="499" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W499" s="7"/>
     </row>
-    <row r="500" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="500" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W500" s="7"/>
     </row>
-    <row r="501" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="501" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W501" s="7"/>
     </row>
-    <row r="502" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="502" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W502" s="7"/>
     </row>
-    <row r="503" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="503" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W503" s="7"/>
     </row>
-    <row r="504" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="504" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W504" s="7"/>
     </row>
-    <row r="505" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="505" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W505" s="7"/>
     </row>
-    <row r="506" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="506" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W506" s="7"/>
     </row>
-    <row r="507" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="507" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W507" s="7"/>
     </row>
-    <row r="508" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="508" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W508" s="7"/>
     </row>
-    <row r="509" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="509" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W509" s="7"/>
     </row>
-    <row r="510" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="510" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W510" s="7"/>
     </row>
-    <row r="511" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="511" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W511" s="7"/>
     </row>
-    <row r="512" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="512" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W512" s="7"/>
     </row>
-    <row r="513" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="513" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W513" s="7"/>
     </row>
-    <row r="514" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="514" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W514" s="7"/>
     </row>
-    <row r="515" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="515" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W515" s="7"/>
     </row>
-    <row r="516" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="516" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W516" s="7"/>
     </row>
-    <row r="517" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="517" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W517" s="7"/>
     </row>
-    <row r="518" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="518" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W518" s="7"/>
     </row>
-    <row r="519" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="519" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W519" s="7"/>
     </row>
-    <row r="520" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="520" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W520" s="7"/>
     </row>
-    <row r="521" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="521" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W521" s="7"/>
     </row>
-    <row r="522" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="522" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W522" s="7"/>
     </row>
-    <row r="523" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="523" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W523" s="7"/>
     </row>
-    <row r="524" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="524" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W524" s="7"/>
     </row>
-    <row r="525" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="525" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W525" s="7"/>
     </row>
-    <row r="526" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="526" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W526" s="7"/>
     </row>
-    <row r="527" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="527" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W527" s="7"/>
     </row>
-    <row r="528" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="528" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W528" s="7"/>
     </row>
-    <row r="529" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="529" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W529" s="7"/>
     </row>
-    <row r="530" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="530" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W530" s="7"/>
     </row>
-    <row r="531" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="531" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W531" s="7"/>
     </row>
-    <row r="532" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="532" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W532" s="7"/>
     </row>
-    <row r="533" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="533" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W533" s="7"/>
     </row>
-    <row r="534" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="534" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W534" s="7"/>
     </row>
-    <row r="535" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="535" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W535" s="7"/>
     </row>
   </sheetData>
@@ -7293,44 +7288,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A7248B-FC5F-481F-A206-5035B67EFB69}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -7343,18 +7338,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G960"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="15" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" customWidth="1"/>
-    <col min="3" max="3" width="33.81640625" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
     <col min="4" max="4" width="102" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>114</v>
       </c>
@@ -7374,7 +7369,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -7388,7 +7383,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
@@ -7402,7 +7397,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>50</v>
       </c>
@@ -7416,7 +7411,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>53</v>
       </c>
@@ -7430,7 +7425,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>54</v>
       </c>
@@ -7444,7 +7439,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>55</v>
       </c>
@@ -7458,7 +7453,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>52</v>
       </c>
@@ -7472,7 +7467,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>49</v>
       </c>
@@ -7486,7 +7481,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>136</v>
       </c>
@@ -7500,7 +7495,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>93</v>
       </c>
@@ -7514,7 +7509,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>102</v>
       </c>
@@ -7528,7 +7523,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>103</v>
       </c>
@@ -7542,7 +7537,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>104</v>
       </c>
@@ -7556,7 +7551,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>105</v>
       </c>
@@ -7570,951 +7565,951 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:G10" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8525,14 +8520,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" customWidth="1"/>
-    <col min="3" max="6" width="8.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="6" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>39</v>
       </c>
@@ -8540,7 +8535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>148</v>
       </c>
@@ -8548,7 +8543,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>149</v>
       </c>
@@ -8556,1006 +8551,1006 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9576,18 +9571,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -9851,6 +9834,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
@@ -9860,23 +9855,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9895,6 +9873,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\darcast\src\git-hub\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F30AC82-67C2-47D9-95E2-39C7B53FE613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFFBCF3-A71C-4D95-BA74-B6EC0DE73031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">Prima dell'invio del referto viene effettuata la validazione dei dati del referto,  permettendo una correzione prima dell'invio del referto. </t>
   </si>
   <si>
-    <t>2026-03-26T15:05:44.710Z</t>
-  </si>
-  <si>
-    <t>5f240523db09769b2e1a112c74ac96ce</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.1.0fb1500ecf47cec8ffb9c5312b85ea027118c7e7e62869e4b2a17eaa97bcfe7f.7ae4522e1f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>Il software non gestisce la storia clinica e le allegie</t>
+  </si>
+  <si>
+    <t>3d0ebf26ce68b2ccd5f4dad228406959</t>
+  </si>
+  <si>
+    <t>2026-03-31T15:02:42.270Z</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.3b6a4c22308c452911b141d984dc5c2a72ca611c6b68257cfb546a84def6795d.812c5223d2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4158,16 +4158,16 @@
         <v>97</v>
       </c>
       <c r="F30" s="32">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="G30" s="32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H30" s="32" t="s">
         <v>184</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J30" s="33" t="s">
         <v>59</v>
@@ -4215,7 +4215,7 @@
         <v>113</v>
       </c>
       <c r="L31" s="33" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
@@ -9562,12 +9562,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9835,21 +9838,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9874,18 +9883,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\darcast\src\git-hub\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFFBCF3-A71C-4D95-BA74-B6EC0DE73031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289E76B9-9B66-4CAA-BC46-BB268F85A942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,13 +809,13 @@
     <t>Il software non gestisce la storia clinica e le allegie</t>
   </si>
   <si>
-    <t>3d0ebf26ce68b2ccd5f4dad228406959</t>
-  </si>
-  <si>
-    <t>2026-03-31T15:02:42.270Z</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.1.3b6a4c22308c452911b141d984dc5c2a72ca611c6b68257cfb546a84def6795d.812c5223d2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-02T09:12:06.717Z</t>
+  </si>
+  <si>
+    <t>5a13db8201200b23dd3f887ea81699c9</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.87bd96acfd2e31503b6694011a6be68881222b79145591c9be3b76d3b7029194.f8d72f1848^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -3374,7 +3374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="50" customFormat="1" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" s="50" customFormat="1" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>76</v>
       </c>
@@ -4158,13 +4158,13 @@
         <v>97</v>
       </c>
       <c r="F30" s="32">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="G30" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H30" s="32" t="s">
         <v>185</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>184</v>
       </c>
       <c r="I30" s="37" t="s">
         <v>186</v>
@@ -9562,18 +9562,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -9837,6 +9825,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9847,23 +9847,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9882,6 +9865,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>

--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\darcast\src\git-hub\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289E76B9-9B66-4CAA-BC46-BB268F85A942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222EB675-B280-4A54-B5AC-031F4DC61D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -809,13 +809,13 @@
     <t>Il software non gestisce la storia clinica e le allegie</t>
   </si>
   <si>
-    <t>2026-04-02T09:12:06.717Z</t>
-  </si>
-  <si>
-    <t>5a13db8201200b23dd3f887ea81699c9</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.1.87bd96acfd2e31503b6694011a6be68881222b79145591c9be3b76d3b7029194.f8d72f1848^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-07T18:32:32.899Z</t>
+  </si>
+  <si>
+    <t>bdb4277fcb95222533a1fdc6b1c47c6d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.b200ff8f52bde9816d554c83cbad43338291415dd2602c189424605934866de6.0b1639d23a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4158,7 +4158,7 @@
         <v>97</v>
       </c>
       <c r="F30" s="32">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="G30" s="32" t="s">
         <v>184</v>
@@ -9562,6 +9562,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -9825,18 +9837,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9847,6 +9847,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9865,23 +9882,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
